--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T14:14:01+00:00</t>
+    <t>2026-10-06T20:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T20:02:10+00:00</t>
+    <t>2026-10-07T08:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:37:44+00:00</t>
+    <t>2026-10-07T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T09:51:04+00:00</t>
+    <t>2026-10-08T08:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T08:06:17+00:00</t>
+    <t>2026-10-08T10:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T10:07:19+00:00</t>
+    <t>2026-10-08T14:58:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:58:47+00:00</t>
+    <t>2026-10-12T13:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-naissance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:25:25+00:00</t>
+    <t>2026-10-14T12:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
